--- a/docs/pension_data_combined_2026-07-31.xlsx
+++ b/docs/pension_data_combined_2026-07-31.xlsx
@@ -1246,7 +1246,7 @@
         <v>2.1466</v>
       </c>
       <c r="D49" t="n">
-        <v>68724974.03</v>
+        <v>68724356.67</v>
       </c>
     </row>
     <row r="50">
@@ -1264,7 +1264,7 @@
         <v>2.1655</v>
       </c>
       <c r="D50" t="n">
-        <v>225435869.7</v>
+        <v>225440609.3</v>
       </c>
     </row>
     <row r="51">
@@ -1282,7 +1282,7 @@
         <v>2.1818</v>
       </c>
       <c r="D51" t="n">
-        <v>345788897.95</v>
+        <v>345758926.2</v>
       </c>
     </row>
     <row r="52">
@@ -1300,7 +1300,7 @@
         <v>2.1823</v>
       </c>
       <c r="D52" t="n">
-        <v>422398367.94</v>
+        <v>422382199.5</v>
       </c>
     </row>
     <row r="53">
@@ -1318,7 +1318,7 @@
         <v>1.9649</v>
       </c>
       <c r="D53" t="n">
-        <v>391975385.87</v>
+        <v>391916393.4</v>
       </c>
     </row>
     <row r="54">
@@ -1336,7 +1336,7 @@
         <v>1.5396</v>
       </c>
       <c r="D54" t="n">
-        <v>326189277.56</v>
+        <v>325897025.9</v>
       </c>
     </row>
     <row r="55">
@@ -1354,7 +1354,7 @@
         <v>1.2016</v>
       </c>
       <c r="D55" t="n">
-        <v>60682211.34</v>
+        <v>60616108.71</v>
       </c>
     </row>
   </sheetData>
